--- a/data/trans_camb/IQ2606_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27,68</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>23,84</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22,68</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,57</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,22</t>
+          <t>22,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,12</t>
+          <t>24,75</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 34,06</t>
+          <t>20,46; 42,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 35,76</t>
+          <t>12,86; 41,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,16; 42,45</t>
+          <t>12,58; 34,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 39,73</t>
+          <t>7,42; 35,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 35,2</t>
+          <t>20,18; 35,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 33,09</t>
+          <t>13,12; 34,14</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>39,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>60,36%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,21; 63,45</t>
+          <t>34,01; 95,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 65,6</t>
+          <t>22,24; 90,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 94,01</t>
+          <t>18,32; 64,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 87,4</t>
+          <t>12,36; 65,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 69,2</t>
+          <t>32,19; 68,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,79; 62,82</t>
+          <t>20,49; 64,88</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24,13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>9,17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,59</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,21</t>
+          <t>13,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,46</t>
+          <t>18,43</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 18,87</t>
+          <t>-2,99; 16,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 25,77</t>
+          <t>7,29; 32,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 17,48</t>
+          <t>-1,42; 19,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 33,97</t>
+          <t>-3,71; 25,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 15,7</t>
+          <t>0,49; 14,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 27,01</t>
+          <t>6,57; 26,6</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>13,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 30,09</t>
+          <t>-3,88; 25,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 40,94</t>
+          <t>10,63; 51,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 28,54</t>
+          <t>-1,92; 31,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 53,94</t>
+          <t>-4,85; 39,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 24,8</t>
+          <t>0,66; 23,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 41,81</t>
+          <t>9,51; 41,04</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30,02</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10,9</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30,98</t>
+          <t>10,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,04</t>
+          <t>21,54</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 13,25</t>
+          <t>-1,18; 22,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 29,97</t>
+          <t>11,81; 41,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 22,83</t>
+          <t>-12,04; 15,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 41,5</t>
+          <t>-18,42; 28,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 14,79</t>
+          <t>-2,32; 15,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 32,83</t>
+          <t>5,82; 33,06</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 24,02</t>
+          <t>-1,86; 40,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 50,77</t>
+          <t>19,28; 76,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 41,01</t>
+          <t>-17,48; 26,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21,02; 75,1</t>
+          <t>-27,78; 48,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 26,0</t>
+          <t>-3,48; 27,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 57,02</t>
+          <t>9,09; 56,52</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>10,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25,28</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15,48</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38,34</t>
+          <t>24,76</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,29</t>
+          <t>32,23</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 17,5</t>
+          <t>7,85; 23,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,63; 34,39</t>
+          <t>29,45; 46,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 23,34</t>
+          <t>2,08; 16,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28,84; 45,6</t>
+          <t>12,06; 34,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 18,04</t>
+          <t>7,56; 18,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 37,96</t>
+          <t>25,2; 38,3</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70,58%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>15,97%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>40,36%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 29,56</t>
+          <t>13,52; 45,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,09; 59,65</t>
+          <t>50,52; 92,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,7; 46,94</t>
+          <t>3,42; 29,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,1; 90,49</t>
+          <t>19,02; 58,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,32; 32,0</t>
+          <t>12,36; 34,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,97; 69,63</t>
+          <t>41,65; 68,23</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16,98</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27,4</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>8,02</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>30,98</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>16,98</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28,2</t>
+          <t>28,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,5</t>
+          <t>26,87</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 16,78</t>
+          <t>7,49; 26,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,22; 41,77</t>
+          <t>12,65; 39,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 26,61</t>
+          <t>-3,15; 17,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,28; 39,21</t>
+          <t>12,45; 40,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 18,79</t>
+          <t>5,75; 19,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,07; 37,13</t>
+          <t>14,9; 34,96</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>32,5%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>52,44%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>14,13%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>32,5%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 32,15</t>
+          <t>12,39; 57,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29,91; 81,55</t>
+          <t>22,77; 82,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14,43; 57,04</t>
+          <t>-5,26; 33,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23,1; 82,28</t>
+          <t>21,39; 80,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,04; 36,42</t>
+          <t>9,82; 37,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,4; 73,4</t>
+          <t>26,49; 66,88</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>14,67</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>32,54</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>14,89</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>17,1</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>14,67</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33,12</t>
+          <t>15,9</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,05</t>
+          <t>25,8</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 28,17</t>
+          <t>2,21; 29,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 35,97</t>
+          <t>12,31; 45,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,91; 27,92</t>
+          <t>-0,29; 28,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14,14; 46,62</t>
+          <t>-18,78; 37,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,45; 24,77</t>
+          <t>5,01; 24,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,7; 38,67</t>
+          <t>10,01; 38,42</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>24,97%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>28,68%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,48; 55,93</t>
+          <t>2,35; 60,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 69,57</t>
+          <t>23,24; 101,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2,39; 62,54</t>
+          <t>-0,15; 58,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>26,26; 102,11</t>
+          <t>-26,0; 69,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,51; 49,15</t>
+          <t>7,97; 47,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,56; 75,16</t>
+          <t>17,19; 74,04</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>16,24</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>29,87</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>10,89</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>22,02</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>16,24</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29,94</t>
+          <t>21,03</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,26</t>
+          <t>25,76</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,87</t>
+          <t>11,85; 20,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14,95; 27,16</t>
+          <t>24,75; 35,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12,41; 20,1</t>
+          <t>6,64; 15,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24,25; 34,99</t>
+          <t>14,27; 26,77</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,89</t>
+          <t>10,66; 16,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,19; 29,94</t>
+          <t>21,37; 29,68</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>52,56%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>17,63%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>28,57%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,45; 25,15</t>
+          <t>19,92; 36,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>23,86; 45,33</t>
+          <t>42,79; 65,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21,09; 37,1</t>
+          <t>10,38; 25,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41,31; 64,03</t>
+          <t>22,51; 44,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,81; 29,18</t>
+          <t>17,67; 29,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,41; 51,54</t>
+          <t>35,45; 51,22</t>
         </is>
       </c>
     </row>
